--- a/Smaers_etal_2017/comparison/cortical surfaces Brodmann 1909 in Smears et al 2017.xlsx
+++ b/Smaers_etal_2017/comparison/cortical surfaces Brodmann 1909 in Smears et al 2017.xlsx
@@ -718,8 +718,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -972,6 +972,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64934DD1-94AD-4949-B1A9-E368BBBB14CF}">
   <ds:schemaRefs>
@@ -981,20 +992,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6869AFDE-D4AB-48CE-BFAF-0898636D3C75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B18D8A9-436F-4306-96A1-0AEB38B36F5C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6B7D253-9482-489C-B80C-03791A844DF2}"/>
 </file>